--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486835_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486835_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6554</v>
+        <v>5.7801</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4098</v>
+        <v>4.9631</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2456</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8281</v>
+        <v>3.4082</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0346</v>
+        <v>2.938</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7934</v>
+        <v>0.4702</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0847</v>
+        <v>4.4297</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3115</v>
+        <v>3.6973</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7732</v>
+        <v>0.7325</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2566</v>
+        <v>-1.0215</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2769</v>
+        <v>-0.7593</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0203</v>
+        <v>-0.2623</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5792</v>
+        <v>2.7031</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7031</v>
+        <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2907</v>
+        <v>-0.3312</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8198</v>
+        <v>0.4409</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5291</v>
+        <v>-0.772</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3709</v>
+        <v>0.2856</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3282</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3609</v>
+        <v>4.9577</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4943</v>
+        <v>2.6376</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8667</v>
+        <v>2.3201</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4082</v>
+        <v>3.8281</v>
       </c>
       <c r="H3" t="n">
-        <v>2.938</v>
+        <v>3.0346</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4702</v>
+        <v>0.7934</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4297</v>
+        <v>4.0847</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6973</v>
+        <v>3.3115</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7325</v>
+        <v>0.7732</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0215</v>
+        <v>-0.2566</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7593</v>
+        <v>-0.2769</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2623</v>
+        <v>0.0203</v>
       </c>
       <c r="P3" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2.1239</v>
+      </c>
+      <c r="R3" t="n">
         <v>2.7031</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.1931</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.8962</v>
-      </c>
       <c r="S3" t="n">
-        <v>-0.7504</v>
+        <v>0.593</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.028</v>
+        <v>1.0476</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7224</v>
+        <v>-0.4546</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5058</v>
+        <v>2.7088</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3469</v>
+        <v>2.9471</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8411</v>
+        <v>-0.2383</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5323</v>
+        <v>1.6894</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9378</v>
+        <v>0.8214</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.4701</v>
+        <v>0.8681</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3243</v>
+        <v>2.4284</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3523</v>
+        <v>1.167</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.6765</v>
+        <v>1.2615</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.208</v>
+        <v>-0.739</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4145</v>
+        <v>-0.3456</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7935</v>
+        <v>-0.3934</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7099</v>
+        <v>0.2897</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1233</v>
+        <v>0.2065</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4134</v>
+        <v>0.0832</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1698</v>
+        <v>-0.0426</v>
       </c>
       <c r="W4" t="n">
-        <v>2.741</v>
+        <v>1.4707</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5712</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8441</v>
+        <v>2.5475</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6851</v>
+        <v>3.2645</v>
       </c>
       <c r="F5" t="n">
-        <v>0.159</v>
+        <v>-0.7169</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6894</v>
+        <v>-1.5323</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8214</v>
+        <v>1.9378</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8681</v>
+        <v>-3.4701</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4284</v>
+        <v>-0.3243</v>
       </c>
       <c r="K5" t="n">
-        <v>1.167</v>
+        <v>2.3523</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2615</v>
+        <v>-2.6765</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.739</v>
+        <v>-1.208</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3456</v>
+        <v>-0.4145</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3934</v>
+        <v>-0.7935</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.425</v>
+        <v>0.7516</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0555</v>
+        <v>1.0408</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4805</v>
+        <v>-0.2892</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0426</v>
+        <v>2.1698</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4707</v>
+        <v>2.741</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5133</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7124</v>
+        <v>1.8392</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4216</v>
+        <v>0.3575</v>
       </c>
       <c r="F6" t="n">
-        <v>1.134</v>
+        <v>1.4817</v>
       </c>
       <c r="G6" t="n">
         <v>0.4362</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2025</v>
+        <v>-0.0757</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4416</v>
+        <v>0.3376</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7609</v>
+        <v>-0.4133</v>
       </c>
       <c r="V6" t="n">
         <v>0.8995</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5906</v>
+        <v>0.6747</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0983</v>
+        <v>0.0603</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6889</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3055</v>
@@ -1000,13 +1000,13 @@
         <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1158</v>
+        <v>0.1999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.11</v>
+        <v>0.2686</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0058</v>
+        <v>-0.0687</v>
       </c>
       <c r="V7" t="n">
         <v>0.0426</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6218</v>
+        <v>-0.5813</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6233</v>
+        <v>1.0816</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2451</v>
+        <v>-1.6629</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.922</v>
+        <v>1.3359</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5513</v>
+        <v>1.6478</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3707</v>
+        <v>-0.3119</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1831</v>
+        <v>1.937</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0679</v>
+        <v>2.1313</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1152</v>
+        <v>-0.1943</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7388</v>
+        <v>-0.6011</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4833</v>
+        <v>-0.4835</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2555</v>
+        <v>-0.1176</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5625</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5441</v>
+        <v>0.3031</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9816</v>
+        <v>-1.1856</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.6831</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9448</v>
+        <v>-0.9008</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1755</v>
+        <v>-2.8583</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2307</v>
+        <v>1.9575</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4353</v>
@@ -1156,13 +1156,13 @@
         <v>2.1239</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2595</v>
+        <v>0.3035</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3857</v>
+        <v>0.7029</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1262</v>
+        <v>-0.3994</v>
       </c>
       <c r="V9" t="n">
         <v>3.3548</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4638</v>
+        <v>-1.0878</v>
       </c>
       <c r="E10" t="n">
-        <v>0.199</v>
+        <v>3.058</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6629</v>
+        <v>-4.1457</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3359</v>
+        <v>-0.922</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6478</v>
+        <v>-0.5513</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3119</v>
+        <v>-0.3707</v>
       </c>
       <c r="J10" t="n">
-        <v>1.937</v>
+        <v>-0.1831</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1313</v>
+        <v>-0.0679</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1943</v>
+        <v>-0.1152</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6011</v>
+        <v>-0.7388</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4835</v>
+        <v>-0.4833</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1176</v>
+        <v>-0.2555</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7651</v>
+        <v>0.0965</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5795</v>
+        <v>0.9788</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1856</v>
+        <v>-0.8823</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2277</v>
+        <v>-3.6831</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.782</v>
+        <v>-1.5296</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6698</v>
+        <v>0.7732</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4518</v>
+        <v>-2.3028</v>
       </c>
       <c r="G11" t="n">
         <v>0.3605</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2318</v>
+        <v>0.0206</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1932</v>
+        <v>-0.0898</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0386</v>
+        <v>0.1104</v>
       </c>
       <c r="V11" t="n">
         <v>-3.0692</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8568</v>
+        <v>14.4085</v>
       </c>
       <c r="E12" t="n">
-        <v>15.7328</v>
+        <v>16.2846</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.876</v>
+        <v>-1.8759</v>
       </c>
       <c r="G12" t="n">
-        <v>4.863199999999999</v>
+        <v>4.8632</v>
       </c>
       <c r="H12" t="n">
         <v>10.3453</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.482</v>
+        <v>-5.482000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>10.8735</v>
@@ -1372,7 +1372,7 @@
         <v>-2.2374</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.010199999999999</v>
+        <v>-6.0102</v>
       </c>
       <c r="N12" t="n">
         <v>-2.7657</v>
@@ -1390,13 +1390,13 @@
         <v>18.3425</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4136000000000004</v>
+        <v>0.9653</v>
       </c>
       <c r="T12" t="n">
-        <v>4.6851</v>
+        <v>5.237</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.271500000000001</v>
+        <v>-4.2715</v>
       </c>
       <c r="V12" t="n">
         <v>0.8568999999999996</v>
@@ -1405,7 +1405,7 @@
         <v>10.7934</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.936699999999998</v>
+        <v>-9.9367</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4306</v>
+        <v>2.1512</v>
       </c>
       <c r="E13" t="n">
-        <v>6.764</v>
+        <v>4.3853</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3334</v>
+        <v>-2.2341</v>
       </c>
       <c r="G13" t="n">
         <v>0.2993</v>
@@ -1468,13 +1468,13 @@
         <v>0.7723</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4515</v>
+        <v>2.1721</v>
       </c>
       <c r="T13" t="n">
-        <v>4.6056</v>
+        <v>2.2269</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1542</v>
+        <v>-0.0548</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8995</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8519</v>
+        <v>1.9469</v>
       </c>
       <c r="E14" t="n">
-        <v>1.395</v>
+        <v>2.0156</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5431</v>
+        <v>-0.0687</v>
       </c>
       <c r="G14" t="n">
         <v>2.4708</v>
@@ -1546,13 +1546,13 @@
         <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9157999999999999</v>
+        <v>0.1792</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1934</v>
+        <v>0.4271</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7224</v>
+        <v>-0.2479</v>
       </c>
       <c r="V14" t="n">
         <v>1.2277</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4756</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.627</v>
+        <v>1.0407</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1026</v>
+        <v>-0.9536</v>
       </c>
       <c r="G15" t="n">
         <v>1.1646</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5903</v>
+        <v>-0.0276</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2759</v>
+        <v>0.1378</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3144</v>
+        <v>-0.1654</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8568</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. JENKINS BAFFOUR</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3595</v>
+        <v>-0.4681</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4582</v>
+        <v>-0.6533</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9013</v>
+        <v>0.1852</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.5301</v>
+        <v>1.3179</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.152</v>
+        <v>-0.242</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.3782</v>
+        <v>1.5598</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.5155</v>
+        <v>1.7123</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4693</v>
+        <v>0.4486</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9848</v>
+        <v>1.2637</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0146</v>
+        <v>-0.3945</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6212</v>
+        <v>-0.6906</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3934</v>
+        <v>0.2961</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1931</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1585</v>
+        <v>-2.8962</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3058</v>
+        <v>-0.2414</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9302</v>
+        <v>0.5305</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3756</v>
+        <v>-0.7719</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5261</v>
+        <v>-1.6061</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6392</v>
+        <v>2.4324</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.1653</v>
+        <v>-4.0385</v>
       </c>
       <c r="G17" t="n">
         <v>1.4315</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9544</v>
+        <v>-1.0344</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.359</v>
+        <v>-0.5658</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5954</v>
+        <v>-0.4686</v>
       </c>
       <c r="V17" t="n">
         <v>-3.3548</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>A. JENKINS BAFFOUR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5783</v>
+        <v>-2.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3773</v>
+        <v>-1.389</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.201</v>
+        <v>-1.1111</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3179</v>
+        <v>-2.5301</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.242</v>
+        <v>-0.152</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5598</v>
+        <v>-2.3782</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7123</v>
+        <v>-1.5155</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4486</v>
+        <v>0.4693</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2637</v>
+        <v>-1.9848</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3945</v>
+        <v>-1.0146</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6906</v>
+        <v>-0.6212</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2961</v>
+        <v>-0.3934</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5446</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8962</v>
+        <v>-1.1585</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3515</v>
+        <v>1.1652</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1934</v>
+        <v>0.9994</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1581</v>
+        <v>0.1658</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. SECK DIOP</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.2047</v>
+        <v>-3.6089</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4022</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8025</v>
+        <v>-2.6568</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0362</v>
+        <v>-1.6876</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.6759</v>
+        <v>-2.8903</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6397</v>
+        <v>1.2027</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9931</v>
+        <v>0.8316</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6058</v>
+        <v>-0.4751</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6127</v>
+        <v>1.3067</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0431</v>
+        <v>-2.5192</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0702</v>
+        <v>-2.4151</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0271</v>
+        <v>-0.1041</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.4754</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.827</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>0.508</v>
+        <v>-0.9792</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6616</v>
+        <v>-0.1385</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1536</v>
+        <v>-0.8407</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7989</v>
+        <v>-0.9421</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7563</v>
+        <v>0.2856</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0426</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5851</v>
+        <v>-3.926</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1186</v>
+        <v>-1.4981</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4665</v>
+        <v>-2.4279</v>
       </c>
       <c r="G20" t="n">
         <v>-4.2935</v>
@@ -2014,13 +2014,13 @@
         <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0866</v>
+        <v>-0.4275</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5245</v>
+        <v>0.096</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5235</v>
       </c>
       <c r="V20" t="n">
         <v>3.1118</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>K. SECK DIOP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.41</v>
+        <v>-4.5538</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1931</v>
+        <v>-3.5056</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2168</v>
+        <v>-1.0482</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6876</v>
+        <v>-3.0362</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.8903</v>
+        <v>-3.6759</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2027</v>
+        <v>0.6397</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8316</v>
+        <v>-0.9931</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4751</v>
+        <v>-1.6058</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3067</v>
+        <v>0.6127</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5192</v>
+        <v>-2.0431</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.4151</v>
+        <v>-2.0702</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1041</v>
+        <v>0.0271</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-3.4754</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-4.827</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.7803</v>
+        <v>0.1589</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3796</v>
+        <v>0.5582</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4007</v>
+        <v>-0.3993</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9421</v>
+        <v>1.7989</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2856</v>
+        <v>1.7563</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="22">
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.8568</v>
+        <v>-12.4778</v>
       </c>
       <c r="E22" t="n">
-        <v>1.875800000000001</v>
+        <v>1.8759</v>
       </c>
       <c r="F22" t="n">
-        <v>-15.7325</v>
+        <v>-14.3537</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.863299999999999</v>
+        <v>-4.8633</v>
       </c>
       <c r="H22" t="n">
         <v>-10.3453</v>
@@ -2146,10 +2146,10 @@
         <v>6.010199999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>2.765800000000001</v>
+        <v>2.765799999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>3.2443</v>
+        <v>3.244300000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-10.8735</v>
@@ -2170,19 +2170,19 @@
         <v>10.6192</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4135999999999993</v>
+        <v>0.9652999999999998</v>
       </c>
       <c r="T22" t="n">
         <v>4.2716</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.6852</v>
+        <v>-3.3063</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8568999999999999</v>
+        <v>-0.8568999999999998</v>
       </c>
       <c r="W22" t="n">
-        <v>9.9367</v>
+        <v>9.936699999999998</v>
       </c>
       <c r="X22" t="n">
         <v>-10.7935</v>
